--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/TEXAS_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/TEXAS_2014.xlsx
@@ -841,7 +841,7 @@
         <v>18</v>
       </c>
       <c r="D27">
-        <v>9.0284848698E-05</v>
+        <v>9.028484869800001E-05</v>
       </c>
     </row>
     <row r="28">
@@ -1327,7 +1327,7 @@
         <v>18</v>
       </c>
       <c r="D54">
-        <v>9.0284848698E-05</v>
+        <v>9.028484869800001E-05</v>
       </c>
     </row>
     <row r="55">
@@ -1417,7 +1417,7 @@
         <v>18</v>
       </c>
       <c r="D59">
-        <v>9.0284848698E-05</v>
+        <v>9.028484869800001E-05</v>
       </c>
     </row>
     <row r="60">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C179">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C189">
@@ -3901,7 +3901,7 @@
         <v>18</v>
       </c>
       <c r="D197">
-        <v>9.0284848698E-05</v>
+        <v>9.028484869800001E-05</v>
       </c>
     </row>
     <row r="198">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C254">
@@ -6475,7 +6475,7 @@
         <v>18</v>
       </c>
       <c r="D340">
-        <v>9.0284848698E-05</v>
+        <v>9.028484869800001E-05</v>
       </c>
     </row>
     <row r="341">
@@ -7303,7 +7303,7 @@
         <v>18</v>
       </c>
       <c r="D386">
-        <v>9.0284848698E-05</v>
+        <v>9.028484869800001E-05</v>
       </c>
     </row>
     <row r="387">
@@ -7501,7 +7501,7 @@
         <v>18</v>
       </c>
       <c r="D397">
-        <v>9.0284848698E-05</v>
+        <v>9.028484869800001E-05</v>
       </c>
     </row>
     <row r="398">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C409">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C419">
@@ -11731,7 +11731,7 @@
         <v>18</v>
       </c>
       <c r="D632">
-        <v>9.0284848698E-05</v>
+        <v>9.028484869800001E-05</v>
       </c>
     </row>
     <row r="633">
@@ -12487,7 +12487,7 @@
         <v>18</v>
       </c>
       <c r="D674">
-        <v>9.0284848698E-05</v>
+        <v>9.028484869800001E-05</v>
       </c>
     </row>
     <row r="675">
@@ -15601,7 +15601,7 @@
         <v>18</v>
       </c>
       <c r="D847">
-        <v>9.0284848698E-05</v>
+        <v>9.028484869800001E-05</v>
       </c>
     </row>
     <row r="848">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C907">
@@ -17077,7 +17077,7 @@
         <v>18</v>
       </c>
       <c r="D929">
-        <v>9.0284848698E-05</v>
+        <v>9.028484869800001E-05</v>
       </c>
     </row>
     <row r="930">
@@ -18121,7 +18121,7 @@
         <v>18</v>
       </c>
       <c r="D987">
-        <v>9.0284848698E-05</v>
+        <v>9.028484869800001E-05</v>
       </c>
     </row>
     <row r="988">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C1082">
@@ -20850,7 +20850,7 @@
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1139">
@@ -20868,7 +20868,7 @@
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1140">
@@ -21030,7 +21030,7 @@
       </c>
       <c r="B1149" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C1149">
@@ -22153,7 +22153,7 @@
         <v>18</v>
       </c>
       <c r="D1211">
-        <v>9.0284848698E-05</v>
+        <v>9.028484869800001E-05</v>
       </c>
     </row>
     <row r="1212">
@@ -23575,7 +23575,7 @@
         <v>18</v>
       </c>
       <c r="D1290">
-        <v>9.0284848698E-05</v>
+        <v>9.028484869800001E-05</v>
       </c>
     </row>
     <row r="1291">
@@ -24079,7 +24079,7 @@
         <v>18</v>
       </c>
       <c r="D1318">
-        <v>9.0284848698E-05</v>
+        <v>9.028484869800001E-05</v>
       </c>
     </row>
     <row r="1319">
@@ -24727,7 +24727,7 @@
         <v>18</v>
       </c>
       <c r="D1354">
-        <v>9.0284848698E-05</v>
+        <v>9.028484869800001E-05</v>
       </c>
     </row>
     <row r="1355">
@@ -26563,7 +26563,7 @@
         <v>18</v>
       </c>
       <c r="D1456">
-        <v>9.0284848698E-05</v>
+        <v>9.028484869800001E-05</v>
       </c>
     </row>
     <row r="1457">
@@ -28957,7 +28957,7 @@
         <v>18</v>
       </c>
       <c r="D1589">
-        <v>9.0284848698E-05</v>
+        <v>9.028484869800001E-05</v>
       </c>
     </row>
     <row r="1590">
@@ -29281,7 +29281,7 @@
         <v>18</v>
       </c>
       <c r="D1607">
-        <v>9.0284848698E-05</v>
+        <v>9.028484869800001E-05</v>
       </c>
     </row>
     <row r="1608">
@@ -30678,7 +30678,7 @@
       </c>
       <c r="B1685" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1685">
@@ -31171,7 +31171,7 @@
         <v>18</v>
       </c>
       <c r="D1712">
-        <v>9.0284848698E-05</v>
+        <v>9.028484869800001E-05</v>
       </c>
     </row>
     <row r="1713">
@@ -31398,7 +31398,7 @@
       </c>
       <c r="B1725" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1725">
@@ -31459,7 +31459,7 @@
         <v>18</v>
       </c>
       <c r="D1728">
-        <v>9.0284848698E-05</v>
+        <v>9.028484869800001E-05</v>
       </c>
     </row>
     <row r="1729">
@@ -33385,7 +33385,7 @@
         <v>18</v>
       </c>
       <c r="D1835">
-        <v>9.0284848698E-05</v>
+        <v>9.028484869800001E-05</v>
       </c>
     </row>
     <row r="1836">
@@ -33979,7 +33979,7 @@
         <v>18</v>
       </c>
       <c r="D1868">
-        <v>9.0284848698E-05</v>
+        <v>9.028484869800001E-05</v>
       </c>
     </row>
     <row r="1869">
@@ -34465,7 +34465,7 @@
         <v>18</v>
       </c>
       <c r="D1895">
-        <v>9.0284848698E-05</v>
+        <v>9.028484869800001E-05</v>
       </c>
     </row>
     <row r="1896">
@@ -34638,7 +34638,7 @@
       </c>
       <c r="B1905" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1905">
